--- a/Assets/Excels/DialogueData.xlsx
+++ b/Assets/Excels/DialogueData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Devs\TRPG.Client\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9B5E8D2-57C6-431D-B3A6-24A294050BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{382BEEDA-2856-49EA-89D0-151501E8B47E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DialogueData" sheetId="1" r:id="rId1"/>
@@ -46,10 +46,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>NPC_000</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>D_Tutorial_000</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -75,18 +71,17 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>저기... 들리니?
-소환식에 틀린건 없는데 이상하네.
-다시 감각을 활성화해야 할지도…</t>
+    <t>D_Tutorial_001</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>이제 보이는거야?
-좋아! 움직일 수도 있겠어?</t>
+    <t>나의 부름에 응답해. 계약자
+...
+소환식에 틀린건 없는데 이상하네.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>D_Tutorial_001</t>
+    <t>체셔</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -94,8 +89,14 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>음… 아직까진 단순이동밖에 모를려나~
-괜찮아! 앞으로 차근차근 알아가는거시야~</t>
+    <t>후훗. 역시 내가 소환한 패밀리어야.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>…에?...슬라임?
+킹갓제너럴엠페러마제스티골져스프레셔스뷰리풀하이클래스엘레강스럭셔리지니어스원더풀월드탑클래스 드래곤이 아니라?...
+우으…
+어쩔 수 없지… 계약자, 나 체셔의 명령에 응답하라. 앞으로 이동.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1042,7 +1043,7 @@
   <cols>
     <col min="1" max="1" width="21.19921875" style="2" customWidth="1"/>
     <col min="2" max="2" width="23.19921875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="83.3984375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="115.296875" style="2" customWidth="1"/>
     <col min="4" max="4" width="20.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="19.296875" style="2" customWidth="1"/>
     <col min="6" max="6" width="9.09765625" style="2" customWidth="1"/>
@@ -1069,7 +1070,7 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -1078,36 +1079,36 @@
     </row>
     <row r="3" spans="1:14" ht="52.2">
       <c r="A3" s="13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>5</v>
+      <c r="B3" s="17" t="s">
+        <v>10</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="34.799999999999997">
+    <row r="4" spans="1:14" ht="69.599999999999994">
       <c r="A4" s="13" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>5</v>
+      <c r="B4" s="17" t="s">
+        <v>10</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
@@ -1119,21 +1120,21 @@
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
     </row>
-    <row r="5" spans="1:14" ht="34.799999999999997">
+    <row r="5" spans="1:14">
       <c r="A5" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>13</v>
-      </c>
       <c r="D5" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>

--- a/Assets/Excels/DialogueData.xlsx
+++ b/Assets/Excels/DialogueData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Devs\TRPG.Client\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{382BEEDA-2856-49EA-89D0-151501E8B47E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7734662-DF16-4865-9217-BF8ACE16DDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -75,12 +75,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>나의 부름에 응답해. 계약자
-...
-소환식에 틀린건 없는데 이상하네.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>체셔</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -89,14 +83,25 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>후훗. 역시 내가 소환한 패밀리어야.</t>
+    <t>헛! 벌써 여기까지 쫒아왔어!!!
+이렇게 된 이상!
+슬라임! 물어!
+…
+파…파이팅?</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>…에?...슬라임?
-킹갓제너럴엠페러마제스티골져스프레셔스뷰리풀하이클래스엘레강스럭셔리지니어스원더풀월드탑클래스 드래곤이 아니라?...
-우으…
-어쩔 수 없지… 계약자, 나 체셔의 명령에 응답하라. 앞으로 이동.</t>
+    <t>나의 부름에 응답해. 계약자.
+...
+소환식에 틀린건 없는데 이상하네.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>좋아! 성공했어!!! 후히히 이제 다 쓸어...
+…에?...슬라임?
+...
+킹갓제너럴엠페러마제스티골져스프레셔스뷰리풀하이클래스럭셔리지니어스원더풀월드탑클래스 드래곤 왜 아닌거지.
+우으…</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1082,10 +1087,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>6</v>
@@ -1094,12 +1099,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="69.599999999999994">
+    <row r="4" spans="1:14" ht="87">
       <c r="A4" s="13" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>13</v>
@@ -1120,15 +1125,15 @@
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" ht="87">
       <c r="A5" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>6</v>
